--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/nov-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/nov-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>27691.35</v>
+        <v>27456.82</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25405.85</v>
+        <v>25190.68</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>18687.74</v>
+        <v>18501.24</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>11684.06</v>
+        <v>11567.45</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12669.55</v>
+        <v>12543.1</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13053.22</v>
+        <v>12922.94</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13467.85</v>
+        <v>13333.44</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>17868.92</v>
+        <v>17690.59</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>79030.36</v>
+        <v>78241.62</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>15123.26</v>
+        <v>14972.33</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>29025.08</v>
+        <v>28721.13</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>11360.28</v>
+        <v>11241.31</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>9946.959999999999</v>
+        <v>9892.59</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13172.13</v>
+        <v>13100.13</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>30033.13</v>
+        <v>29868.97</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>12564.01</v>
+        <v>12495.33</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>11511.05</v>
+        <v>11448.13</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>7257.54</v>
+        <v>7217.87</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>12757.04</v>
+        <v>12687.32</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>19144.72</v>
+        <v>18931.42</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9874.200000000001</v>
+        <v>9764.190000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>31090.65</v>
+        <v>30920.39</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>19664.36</v>
+        <v>19556.67</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>38138.6</v>
+        <v>37929.74</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>24335.22</v>
+        <v>24201.95</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6575.1</v>
+        <v>6566.73</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>24535.36</v>
+        <v>24504.13</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>27350.65</v>
+        <v>27315.84</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7881.74</v>
+        <v>7909.87</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7962.4</v>
+        <v>7990.81</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>23341.21</v>
+        <v>23424.51</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>11945.18</v>
+        <v>11987.81</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>27135.43</v>
+        <v>27232.27</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>26836.69</v>
+        <v>27128.58</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12079.76</v>
+        <v>12211.14</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>59175.26</v>
+        <v>59818.87</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8349.700000000001</v>
+        <v>8440.52</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>29324.71</v>
+        <v>29643.66</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>14447.87</v>
+        <v>14605.01</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>10507.43</v>
+        <v>10621.72</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>11066.61</v>
+        <v>11186.97</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7573.59</v>
+        <v>7598.5</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>26283.61</v>
+        <v>26370.06</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10030.3</v>
+        <v>10063.29</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>13883.56</v>
+        <v>13929.23</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>7037.72</v>
+        <v>7060.87</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>6999.47</v>
+        <v>7120.29</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>10473.38</v>
+        <v>10654.16</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>10569.83</v>
+        <v>10752.28</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>12272.64</v>
+        <v>12484.49</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8609.370000000001</v>
+        <v>8757.98</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>20158.82</v>
+        <v>20298.47</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>22824.48</v>
+        <v>22982.6</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>41504</v>
+        <v>41791.52</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>30265.11</v>
+        <v>30406.06</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>12202.38</v>
+        <v>12259.21</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>49853.53</v>
+        <v>50212.95</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5944.24</v>
+        <v>5987.09</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>26661.96</v>
+        <v>26854.18</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>9442.639999999999</v>
+        <v>9425.889999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>17232.29</v>
+        <v>17201.73</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>62042.97</v>
+        <v>61932.94</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>35188.73</v>
+        <v>35126.32</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>58336.15</v>
+        <v>58232.68</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6382.34</v>
+        <v>6371.02</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8273.52</v>
+        <v>8239.42</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>12244.52</v>
+        <v>12194.06</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>27528.92</v>
+        <v>27415.46</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>7569</v>
+        <v>7537.8</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>62921.03</v>
+        <v>62823.5</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>15141.65</v>
+        <v>15118.18</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>14803.32</v>
+        <v>14780.37</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5540.4</v>
+        <v>5531.81</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>13615.3</v>
+        <v>13685.61</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>24222.29</v>
+        <v>24347.39</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>13775.39</v>
+        <v>13846.53</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>12841.88</v>
+        <v>12932.51</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>14339.89</v>
+        <v>14441.1</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5740.17</v>
+        <v>5780.68</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>8619.01</v>
+        <v>8679.84</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/nov-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/nov-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/nov-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/nov-2025.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIO</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA  </t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/nov-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/nov-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1135,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1200,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1265,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1330,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1395,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1460,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1647,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1712,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1838,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1903,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2090,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2155,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2220,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2285,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2350,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2415,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2480,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2545,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2610,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2675,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2592,7 +2692,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2292-9277-CM25</t>
+          <t>3888-661-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2617,37 +2717,41 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12211.14</v>
+        <v>8440.52</v>
       </c>
     </row>
     <row r="37">
@@ -2714,7 +2818,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3888-661-CM25</t>
+          <t>2292-9277-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2739,27 +2843,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.625.647-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,7 +2873,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8440.52</v>
+        <v>12211.14</v>
       </c>
     </row>
     <row r="39">
@@ -2823,7 +2927,11 @@
           <t>77.043.435-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2836,7 +2944,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5520-10738-CM25</t>
+          <t>5520-10734-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2876,12 +2984,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,7 +2999,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>14605.01</v>
+        <v>11186.97</v>
       </c>
     </row>
     <row r="41">
@@ -2945,7 +3053,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2958,7 +3070,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5520-10734-CM25</t>
+          <t>5520-10738-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2998,12 +3110,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.067.326-9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3013,7 +3125,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>11186.97</v>
+        <v>14605.01</v>
       </c>
     </row>
     <row r="43">
@@ -3128,7 +3240,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3305,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3431,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3324,7 +3448,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1460278-223-CM25</t>
+          <t>5510-122-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3344,17 +3468,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3364,12 +3488,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3379,13 +3503,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>7120.29</v>
+        <v>8757.98</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>820-49-CM25</t>
+          <t>1460278-223-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3405,32 +3529,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>76.067.326-9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3440,13 +3564,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>10654.16</v>
+        <v>7120.29</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2409-1784-CM25</t>
+          <t>820-49-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3471,37 +3595,41 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>10752.28</v>
+        <v>10654.16</v>
       </c>
     </row>
     <row r="51">
@@ -3555,7 +3683,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3568,7 +3700,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5510-122-CM25</t>
+          <t>2409-1784-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3593,37 +3725,41 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8757.98</v>
+        <v>10752.28</v>
       </c>
     </row>
     <row r="53">
@@ -3677,7 +3813,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3751,7 +3891,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>692277-123-CM25</t>
+          <t>1375735-81-SE25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3776,43 +3916,47 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>41791.52</v>
+        <v>7303.72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1079516-1465-CM25</t>
+          <t>692277-123-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,7 +3971,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3837,27 +3981,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,7 +4011,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>30406.06</v>
+        <v>41791.52</v>
       </c>
     </row>
     <row r="57">
@@ -3921,7 +4065,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3934,7 +4082,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>507428-3993-CM25</t>
+          <t>1079516-1465-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3949,7 +4097,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3959,37 +4107,41 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>50212.95</v>
+        <v>30406.06</v>
       </c>
     </row>
     <row r="59">
@@ -4043,7 +4195,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4056,7 +4212,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2723-3897-CM25</t>
+          <t>507428-3993-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4076,22 +4232,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.072.500-2</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BUIN</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4104,20 +4260,24 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>26854.18</v>
+        <v>50212.95</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1079580-493-CM25</t>
+          <t>2723-3897-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4132,53 +4292,57 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>69.072.500-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE BUIN</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>9425.889999999999</v>
+        <v>26854.18</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1079580-495-CM25</t>
+          <t>1079580-493-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4218,28 +4382,32 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>17201.73</v>
+        <v>9425.889999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>507428-3992-CM25</t>
+          <t>1079580-495-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4264,43 +4432,47 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>15.888.842-4</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>61932.94</v>
+        <v>17201.73</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1053139-266-CM25</t>
+          <t>507428-3992-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4320,48 +4492,52 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>35126.32</v>
+        <v>61932.94</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5510-125-CM25</t>
+          <t>1053139-266-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4386,43 +4562,47 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>58232.68</v>
+        <v>35126.32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2580-1310-CM25</t>
+          <t>5510-125-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4442,17 +4622,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4462,12 +4642,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4477,13 +4657,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6371.02</v>
+        <v>58232.68</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1475044-17-CM25</t>
+          <t>2580-1310-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4498,7 +4678,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4508,12 +4688,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4523,28 +4703,32 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8239.42</v>
+        <v>6371.02</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1208129-730-CM25</t>
+          <t>1475044-17-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4569,17 +4753,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4592,20 +4776,24 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>12194.06</v>
+        <v>8239.42</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1476007-10-CM25</t>
+          <t>1208129-730-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4630,43 +4818,47 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>27415.46</v>
+        <v>12194.06</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1232366-156-CM25</t>
+          <t>1476007-10-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4686,17 +4878,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4706,28 +4898,32 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>7537.8</v>
+        <v>27415.46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1293138-354-CM25</t>
+          <t>1232366-156-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4742,22 +4938,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4767,28 +4963,32 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>62823.5</v>
+        <v>7537.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1216062-1154-CM25</t>
+          <t>1293138-354-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4808,17 +5008,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>71.265.200-4</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Lo Prado</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4828,28 +5028,32 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rescatelife limitada </t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.217.441-3</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>15118.18</v>
+        <v>62823.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1469101-5-CM25</t>
+          <t>1216062-1154-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4869,48 +5073,52 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>71.265.200-4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>Corporación Municipal de Lo Prado</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t xml:space="preserve">Rescatelife limitada </t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>76.217.441-3</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>14780.37</v>
+        <v>15118.18</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2675-461-CM25</t>
+          <t>1469101-5-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4935,12 +5143,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4950,28 +5158,32 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5531.81</v>
+        <v>14780.37</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5441-799-CM25</t>
+          <t>2675-461-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4986,7 +5198,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4996,43 +5208,47 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>13685.61</v>
+        <v>5531.81</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1293138-353-CM25</t>
+          <t>5441-799-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5057,12 +5273,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5072,12 +5288,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>76.675.854-1</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5087,13 +5303,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>24347.39</v>
+        <v>13685.61</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4238-396-CM25</t>
+          <t>1293138-353-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5118,43 +5334,47 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>13846.53</v>
+        <v>24347.39</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5890-193-CM25</t>
+          <t>4238-396-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5169,7 +5389,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5179,43 +5399,47 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>12932.51</v>
+        <v>13846.53</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2854-1691-CM25</t>
+          <t>5890-193-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5235,48 +5459,52 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>14441.1</v>
+        <v>12932.51</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>594965-216-CM25</t>
+          <t>2854-1691-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5296,102 +5524,175 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5780.68</v>
+        <v>14441.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>594965-216-CM25</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>IGMA CONSULTORES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>76.465.697-0</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>5780.68</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>5740-485-CM25</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>61.979.060-k</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Los Ríos</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>EVENTAIL SPA</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="n">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
         <v>8679.84</v>
       </c>
     </row>
